--- a/서식_온실가스_배출량_산정_템플릿_지수광풍판.xlsx
+++ b/서식_온실가스_배출량_산정_템플릿_지수광풍판.xlsx
@@ -14,6 +14,7 @@
     <sheet name="⑤Scope2_전력" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="⑥종합요약" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="⑦근거조항" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="⑧조회근거" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="FUEL_TABLE">'②배출계수_참조표'!$B$7:$J$13</definedName>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="\+0.000;\-0.000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -249,6 +250,14 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -382,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -530,6 +539,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4200,4 +4219,301 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="72" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>조회 근거 — 이 숫자가 어디서 왔는가</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="92" t="inlineStr">
+        <is>
+          <t>보고서를 받는 쪽과 검증하는 쪽이 반드시 묻는 것입니다. 도구가 자동으로 채웁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="93" t="inlineStr">
+        <is>
+          <t>사찰명</t>
+        </is>
+      </c>
+      <c r="C5" s="94" t="n"/>
+      <c r="D5" s="75" t="n"/>
+      <c r="E5" s="75" t="n"/>
+      <c r="F5" s="75" t="n"/>
+      <c r="G5" s="75" t="n"/>
+      <c r="H5" s="75" t="n"/>
+      <c r="I5" s="76" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>도로명주소</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="n"/>
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="75" t="n"/>
+      <c r="F6" s="75" t="n"/>
+      <c r="G6" s="75" t="n"/>
+      <c r="H6" s="75" t="n"/>
+      <c r="I6" s="76" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="93" t="inlineStr">
+        <is>
+          <t>조회 연도</t>
+        </is>
+      </c>
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="75" t="n"/>
+      <c r="F7" s="75" t="n"/>
+      <c r="G7" s="75" t="n"/>
+      <c r="H7" s="75" t="n"/>
+      <c r="I7" s="76" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="93" t="inlineStr">
+        <is>
+          <t>조회일</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="n"/>
+      <c r="D8" s="75" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="75" t="n"/>
+      <c r="H8" s="75" t="n"/>
+      <c r="I8" s="76" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="93" t="inlineStr">
+        <is>
+          <t>자료 출처</t>
+        </is>
+      </c>
+      <c r="C9" s="94" t="inlineStr">
+        <is>
+          <t>국토교통부 건축HUB 건물에너지 · 건축물대장 (공공데이터포털)</t>
+        </is>
+      </c>
+      <c r="D9" s="75" t="n"/>
+      <c r="E9" s="75" t="n"/>
+      <c r="F9" s="75" t="n"/>
+      <c r="G9" s="75" t="n"/>
+      <c r="H9" s="75" t="n"/>
+      <c r="I9" s="76" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="93" t="inlineStr">
+        <is>
+          <t>한전 계약 확인</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="n"/>
+      <c r="D10" s="75" t="n"/>
+      <c r="E10" s="75" t="n"/>
+      <c r="F10" s="75" t="n"/>
+      <c r="G10" s="75" t="n"/>
+      <c r="H10" s="75" t="n"/>
+      <c r="I10" s="76" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>조회한 지번 (지번마다 한 줄)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="78" t="inlineStr">
+        <is>
+          <t>지번</t>
+        </is>
+      </c>
+      <c r="C13" s="78" t="inlineStr">
+        <is>
+          <t>연면적(m²)</t>
+        </is>
+      </c>
+      <c r="D13" s="78" t="inlineStr">
+        <is>
+          <t>주차장 제외(m²)</t>
+        </is>
+      </c>
+      <c r="E13" s="78" t="inlineStr">
+        <is>
+          <t>전기(kWh)</t>
+        </is>
+      </c>
+      <c r="F13" s="78" t="inlineStr">
+        <is>
+          <t>가스(kWh)</t>
+        </is>
+      </c>
+      <c r="G13" s="78" t="inlineStr">
+        <is>
+          <t>동수</t>
+        </is>
+      </c>
+      <c r="H13" s="78" t="inlineStr">
+        <is>
+          <t>전통</t>
+        </is>
+      </c>
+      <c r="I13" s="78" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="86" t="n"/>
+      <c r="C14" s="86" t="n"/>
+      <c r="D14" s="86" t="n"/>
+      <c r="E14" s="86" t="n"/>
+      <c r="F14" s="86" t="n"/>
+      <c r="G14" s="86" t="n"/>
+      <c r="H14" s="86" t="n"/>
+      <c r="I14" s="86" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="86" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="86" t="n"/>
+      <c r="F15" s="86" t="n"/>
+      <c r="G15" s="86" t="n"/>
+      <c r="H15" s="86" t="n"/>
+      <c r="I15" s="86" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="86" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="86" t="n"/>
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="86" t="n"/>
+      <c r="H16" s="86" t="n"/>
+      <c r="I16" s="86" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="86" t="n"/>
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="86" t="n"/>
+      <c r="H17" s="86" t="n"/>
+      <c r="I17" s="86" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="86" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="86" t="n"/>
+      <c r="F18" s="86" t="n"/>
+      <c r="G18" s="86" t="n"/>
+      <c r="H18" s="86" t="n"/>
+      <c r="I18" s="86" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="86" t="n"/>
+      <c r="D19" s="86" t="n"/>
+      <c r="E19" s="86" t="n"/>
+      <c r="F19" s="86" t="n"/>
+      <c r="G19" s="86" t="n"/>
+      <c r="H19" s="86" t="n"/>
+      <c r="I19" s="86" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="77" t="inlineStr">
+        <is>
+          <t>* 여러 지번을 묶은 경우 합계는 지번별 값의 합입니다. 잰 값의 합이라 한전 계약 수와 상관없이 맞습니다. 다만 **면적당 값**은 계약이 하나로 확인되어야 뜻이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>현장 입력값</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>반영되지 않은 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="77" t="inlineStr">
+        <is>
+          <t>이 엑셀의 합계는 **공개자료로 잡힌 부분의 소계**입니다. 아래는 들어 있지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="77" t="inlineStr">
+        <is>
+          <t>· LPG·등유·화목 (현장에서 안 넣었으면)   · 차량 연료 (안 넣었으면)   · 지역난방 (건물 단위 API 가 주지 않습니다)   · 상수도·폐기물 등 Scope 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="83" t="inlineStr">
+        <is>
+          <t>적용 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="77" t="inlineStr">
+        <is>
+          <t>전력 발전단 0.3844 · GWP AR5(CH4 28 / N2O 265) · CH4·N2O 상업·공공 열 · 도로는 별표6 &lt;표-4&gt; · 환경부고시 제2025-64호</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="B26:I26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>